--- a/resources/script/mapping/sampleMapping/SampleMappings_11.xlsx
+++ b/resources/script/mapping/sampleMapping/SampleMappings_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ck/work/git/cumulocity-dynamic-mapper/resources/script/mapping/sampleMapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A27204A-9C7B-374A-8736-9ED2F98B1AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DA52C2-10A4-0D49-A27A-5DE116B9F1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33920" yWindow="3860" windowWidth="34560" windowHeight="21580" xr2:uid="{B5E387B2-3E90-884E-B546-D827ECD68714}"/>
   </bookViews>
